--- a/artfynd/A 747-2022 artfynd.xlsx
+++ b/artfynd/A 747-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 747-2022 artfynd.xlsx
+++ b/artfynd/A 747-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112234488</v>
+        <v>112234315</v>
       </c>
       <c r="B2" t="n">
-        <v>78778</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kälshöjden (Kälshöjden), Ång</t>
+          <t>Kälshöjden, Kälshöjden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607738</v>
+        <v>607865</v>
       </c>
       <c r="R2" t="n">
-        <v>7043747</v>
+        <v>7043733</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -778,51 +773,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112234449</v>
+        <v>112234852</v>
       </c>
       <c r="B3" t="n">
-        <v>78779</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kälshöjden (Kälshöjden), Ång</t>
+          <t>Kälshöjden, Kälshöjden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607781</v>
+        <v>607741</v>
       </c>
       <c r="R3" t="n">
-        <v>7043736</v>
+        <v>7043940</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -881,51 +871,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112234886</v>
+        <v>112234593</v>
       </c>
       <c r="B4" t="n">
-        <v>89558</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kälshöjden (Kälshöjden), Ång</t>
+          <t>Kälshöjden, Kälshöjden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607750</v>
+        <v>607730</v>
       </c>
       <c r="R4" t="n">
-        <v>7043935</v>
+        <v>7043807</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -984,15 +969,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112234852</v>
+        <v>112234856</v>
       </c>
       <c r="B5" t="n">
-        <v>89875</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,35 +980,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kälshöjden (Kälshöjden), Ång</t>
+          <t>Kälshöjden, Kälshöjden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>607741</v>
       </c>
       <c r="R5" t="n">
-        <v>7043939</v>
+        <v>7043940</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1087,51 +1067,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112234856</v>
+        <v>112234706</v>
       </c>
       <c r="B6" t="n">
-        <v>90034</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kälshöjden (Kälshöjden), Ång</t>
+          <t>Kälshöjden, Kälshöjden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607741</v>
+        <v>607769</v>
       </c>
       <c r="R6" t="n">
-        <v>7043939</v>
+        <v>7043829</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,51 +1165,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112234593</v>
+        <v>112234886</v>
       </c>
       <c r="B7" t="n">
-        <v>89594</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kälshöjden (Kälshöjden), Ång</t>
+          <t>Kälshöjden, Kälshöjden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607729</v>
+        <v>607749</v>
       </c>
       <c r="R7" t="n">
-        <v>7043807</v>
+        <v>7043934</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1293,15 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112234945</v>
+        <v>112234386</v>
       </c>
       <c r="B8" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1309,40 +1274,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kälshöjden (Kälshöjden), Ång</t>
+          <t>Kälshöjden, Kälshöjden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607671</v>
+        <v>607822</v>
       </c>
       <c r="R8" t="n">
-        <v>7043913</v>
+        <v>7043736</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1401,15 +1361,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112234315</v>
+        <v>112234452</v>
       </c>
       <c r="B9" t="n">
-        <v>85891</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1417,35 +1372,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kälshöjden (Kälshöjden), Ång</t>
+          <t>Kälshöjden, Kälshöjden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607865</v>
+        <v>607781</v>
       </c>
       <c r="R9" t="n">
-        <v>7043733</v>
+        <v>7043736</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1504,51 +1459,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112234452</v>
+        <v>112234488</v>
       </c>
       <c r="B10" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kälshöjden (Kälshöjden), Ång</t>
+          <t>Kälshöjden, Kälshöjden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607781</v>
+        <v>607738</v>
       </c>
       <c r="R10" t="n">
-        <v>7043736</v>
+        <v>7043747</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1607,51 +1557,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112234671</v>
+        <v>112234449</v>
       </c>
       <c r="B11" t="n">
-        <v>89612</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kälshöjden (Kälshöjden), Ång</t>
+          <t>Kälshöjden, Kälshöjden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607748</v>
+        <v>607781</v>
       </c>
       <c r="R11" t="n">
-        <v>7043804</v>
+        <v>7043736</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1710,51 +1655,51 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112234706</v>
+        <v>112234945</v>
       </c>
       <c r="B12" t="n">
-        <v>89558</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kälshöjden (Kälshöjden), Ång</t>
+          <t>Kälshöjden, Kälshöjden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607769</v>
+        <v>607671</v>
       </c>
       <c r="R12" t="n">
-        <v>7043830</v>
+        <v>7043913</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1810,6 +1755,109 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112235582</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kälshöjden, Kälshöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>607491</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7044135</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 747-2022 artfynd.xlsx
+++ b/artfynd/A 747-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234315</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234852</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234593</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234856</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234706</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234886</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234386</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234452</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234488</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234449</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1755,6 +1810,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112234945</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1858,8 +1918,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112235582</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>